--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:57:11+00:00</t>
+    <t>2026-09-14T07:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:03:29+00:00</t>
+    <t>2026-09-14T07:11:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:11:51+00:00</t>
+    <t>2026-09-14T07:28:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:28:02+00:00</t>
+    <t>2026-09-14T08:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:01:31+00:00</t>
+    <t>2026-09-14T08:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:17:06+00:00</t>
+    <t>2026-10-09T09:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -14663,7 +14663,7 @@
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ci</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:59:07+00:00</t>
+    <t>2026-10-09T10:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:28:47+00:00</t>
+    <t>2026-10-09T10:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$121</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4319" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4287" uniqueCount="570">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:42:14+00:00</t>
+    <t>2026-10-13T11:58:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1435,8 +1435,8 @@
 Effective TimeOccurrence</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
+    <t>dateTime
+Period</t>
   </si>
   <si>
     <t>Klinisches Bezugsdatum</t>
@@ -1445,7 +1445,8 @@
     <t>Zeitpunkt, zu dem die gemessene Eigenschaft im Probenmaterial (e.g. Analytkonzentration) mutmaßlich der Eigenschaft im Patienten entsprach. 
 Wenn der Zeitpunkt der Probenentnahme angegeben ist, wird meist dieser Zeitpunkt verwendet. 
 Andernfalls wird zumeist behelfsmäßig der Probeneingang im Labor gewählt. 
-Dieses Element ist wichtig um verschiedene Analysen im Zeitverlauf sortieren zu können.</t>
+Dieses Element ist wichtig um verschiedene Analysen im Zeitverlauf sortieren zu können.
+Stammen die Untersuchungen aus mehreren Proben oder wurde eine Probe über einen Zeitraum gewonnen (z. B. 24-Stunden-Sammelurin), ist es ein Zeitraum.</t>
   </si>
   <si>
     <t>If the diagnostic procedure was performed on the patient, this is the time it was performed. If there are specimens, the diagnostically relevant time can be derived from the specimen collection times, but the specimen information is not always available, and the exact relationship between the specimens and the diagnostically relevant time is not always automatic.</t>
@@ -1466,19 +1467,7 @@
     <t>DiagnosticReport.effective[x].id</t>
   </si>
   <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
     <t>DiagnosticReport.effective[x].extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t>DiagnosticReport.effective[x].extension:QuelleKlinischesBezugsdatum</t>
@@ -1495,22 +1484,6 @@
   </si>
   <si>
     <t>Datum der Probenentnahme | Datum des Eingangs der Probe im Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x].value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -2152,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM122"/>
+  <dimension ref="A1:AM121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.33984375" customWidth="true" bestFit="true"/>
@@ -11685,10 +11658,10 @@
         <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>462</v>
+        <v>103</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>463</v>
+        <v>104</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11765,14 +11738,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11794,12 +11767,14 @@
         <v>108</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>465</v>
+        <v>109</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -11838,7 +11813,9 @@
       <c r="AB87" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AC87" s="2"/>
+      <c r="AC87" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
@@ -11872,13 +11849,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B88" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -11900,13 +11877,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11966,7 +11943,7 @@
         <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>116</v>
@@ -11981,44 +11958,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>79</v>
+        <v>469</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>453</v>
+        <v>123</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
       </c>
@@ -12066,7 +12047,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12078,35 +12059,35 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>89</v>
@@ -12118,7 +12099,7 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>123</v>
+        <v>478</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>479</v>
@@ -12179,13 +12160,13 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>79</v>
@@ -12194,57 +12175,53 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>486</v>
+        <v>79</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>487</v>
+        <v>102</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12292,47 +12269,47 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>485</v>
+        <v>105</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>494</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>79</v>
@@ -12344,15 +12321,17 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -12389,31 +12368,31 @@
         <v>79</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
@@ -12425,44 +12404,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>110</v>
+        <v>347</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>111</v>
+        <v>348</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12500,31 +12479,31 @@
         <v>79</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>115</v>
+        <v>349</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
@@ -12536,12 +12515,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12555,7 +12534,7 @@
         <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>79</v>
@@ -12564,16 +12543,16 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12599,13 +12578,13 @@
         <v>79</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>79</v>
@@ -12623,7 +12602,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12632,7 +12611,7 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>100</v>
@@ -12647,12 +12626,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12666,7 +12645,7 @@
         <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>79</v>
@@ -12675,16 +12654,16 @@
         <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12710,13 +12689,13 @@
         <v>79</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>79</v>
@@ -12734,7 +12713,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12758,12 +12737,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12777,7 +12756,7 @@
         <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>79</v>
@@ -12786,16 +12765,16 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12845,7 +12824,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -12871,21 +12850,21 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>79</v>
+        <v>493</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>79</v>
@@ -12897,18 +12876,20 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>102</v>
+        <v>478</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>364</v>
+        <v>494</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>365</v>
+        <v>495</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
       </c>
@@ -12956,13 +12937,13 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>367</v>
+        <v>492</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
@@ -12971,25 +12952,25 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>502</v>
+        <v>79</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -12999,28 +12980,28 @@
         <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O98" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13069,7 +13050,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13084,21 +13065,21 @@
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>494</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13109,10 +13090,10 @@
         <v>77</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>79</v>
@@ -13121,20 +13102,16 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>508</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>509</v>
+        <v>103</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>79</v>
       </c>
@@ -13182,25 +13159,25 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>507</v>
+        <v>105</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>513</v>
+        <v>79</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>79</v>
@@ -13208,21 +13185,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>79</v>
@@ -13234,15 +13211,17 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -13279,31 +13258,31 @@
         <v>79</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
@@ -13315,44 +13294,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>110</v>
+        <v>347</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>111</v>
+        <v>348</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13390,31 +13369,31 @@
         <v>79</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>115</v>
+        <v>349</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
@@ -13426,12 +13405,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13445,7 +13424,7 @@
         <v>88</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>79</v>
@@ -13454,16 +13433,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13489,13 +13468,13 @@
         <v>79</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>79</v>
@@ -13513,7 +13492,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13522,7 +13501,7 @@
         <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>100</v>
@@ -13537,12 +13516,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13556,7 +13535,7 @@
         <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>79</v>
@@ -13565,16 +13544,16 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13600,13 +13579,13 @@
         <v>79</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>79</v>
@@ -13624,7 +13603,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13648,12 +13627,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13667,7 +13646,7 @@
         <v>88</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>79</v>
@@ -13676,16 +13655,16 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13735,7 +13714,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13759,46 +13738,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>79</v>
+        <v>512</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>102</v>
+        <v>513</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>364</v>
+        <v>514</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>365</v>
+        <v>515</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -13846,13 +13827,13 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>367</v>
+        <v>511</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
@@ -13864,32 +13845,32 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>79</v>
+        <v>518</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>521</v>
+        <v>79</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>79</v>
@@ -13898,20 +13879,16 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>522</v>
+        <v>102</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>523</v>
+        <v>103</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
       </c>
@@ -13959,25 +13936,25 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>527</v>
+        <v>79</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>79</v>
@@ -13985,21 +13962,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
@@ -14011,15 +13988,17 @@
         <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -14056,31 +14035,31 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -14092,44 +14071,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>110</v>
+        <v>347</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>111</v>
+        <v>348</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14167,31 +14146,31 @@
         <v>79</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>115</v>
+        <v>349</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>79</v>
@@ -14203,12 +14182,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14222,7 +14201,7 @@
         <v>88</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>79</v>
@@ -14231,16 +14210,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14266,13 +14245,13 @@
         <v>79</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>79</v>
@@ -14290,7 +14269,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14299,7 +14278,7 @@
         <v>88</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>100</v>
@@ -14316,10 +14295,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14342,16 +14321,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14377,13 +14356,13 @@
         <v>79</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>79</v>
@@ -14401,7 +14380,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14427,10 +14406,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14453,16 +14432,16 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14512,7 +14491,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14538,10 +14517,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14552,7 +14531,7 @@
         <v>77</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>79</v>
@@ -14561,19 +14540,19 @@
         <v>79</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>364</v>
+        <v>527</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>365</v>
+        <v>528</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>366</v>
+        <v>529</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14623,13 +14602,13 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>367</v>
+        <v>525</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>79</v>
@@ -14649,21 +14628,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -14672,21 +14651,21 @@
         <v>79</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L113" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>79</v>
       </c>
@@ -14734,7 +14713,7 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -14752,7 +14731,7 @@
         <v>79</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>79</v>
+        <v>536</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>79</v>
@@ -14760,21 +14739,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>540</v>
+        <v>79</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>79</v>
@@ -14783,21 +14762,19 @@
         <v>79</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>541</v>
+        <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>542</v>
+        <v>103</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>543</v>
+        <v>104</v>
       </c>
       <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>544</v>
-      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>79</v>
       </c>
@@ -14845,25 +14822,25 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>539</v>
+        <v>105</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>79</v>
@@ -14871,21 +14848,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>79</v>
@@ -14897,15 +14874,17 @@
         <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -14954,19 +14933,19 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
@@ -14980,14 +14959,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>107</v>
+        <v>540</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15000,24 +14979,26 @@
         <v>79</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>109</v>
+        <v>541</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>110</v>
+        <v>542</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
       </c>
@@ -15065,7 +15046,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>115</v>
+        <v>543</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15091,45 +15072,45 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>111</v>
+        <v>547</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>191</v>
+        <v>548</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
@@ -15178,19 +15159,19 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -15204,10 +15185,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15215,7 +15196,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>88</v>
@@ -15227,23 +15208,19 @@
         <v>79</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>102</v>
+        <v>550</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>79</v>
       </c>
@@ -15291,10 +15268,10 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>88</v>
@@ -15315,44 +15292,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>79</v>
+        <v>554</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>559</v>
+        <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
       </c>
@@ -15400,10 +15379,10 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>88</v>
@@ -15418,32 +15397,32 @@
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>79</v>
+        <v>558</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>563</v>
+        <v>79</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>79</v>
@@ -15452,18 +15431,16 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>566</v>
-      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>79</v>
       </c>
@@ -15487,13 +15464,13 @@
         <v>79</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>79</v>
+        <v>562</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>79</v>
+        <v>563</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>79</v>
@@ -15511,13 +15488,13 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
@@ -15529,7 +15506,7 @@
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>79</v>
@@ -15537,10 +15514,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15563,16 +15540,20 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>225</v>
+        <v>565</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O121" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M121" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>79</v>
       </c>
@@ -15596,13 +15577,13 @@
         <v>79</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>571</v>
+        <v>79</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>572</v>
+        <v>79</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>79</v>
@@ -15620,7 +15601,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15638,127 +15619,14 @@
         <v>79</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AM122" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM122">
+  <autoFilter ref="A1:AM121">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15768,7 +15636,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI121">
+  <conditionalFormatting sqref="A2:AI120">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:58:12+00:00</t>
+    <t>2026-10-13T12:04:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:04:10+00:00</t>
+    <t>2026-10-13T12:10:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:10:53+00:00</t>
+    <t>2026-10-13T12:17:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:17:17+00:00</t>
+    <t>2026-10-13T12:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:41:55+00:00</t>
+    <t>2026-10-13T13:04:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
